--- a/jdm_questions.xlsx
+++ b/jdm_questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Teaching\FA 25 PSY 30400\Experiments\JDM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D572CEA0-66FC-4173-B403-DF7312757947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C3FB47-E403-4D98-A9B0-AFD1C6709AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="130" windowWidth="25600" windowHeight="15150" xr2:uid="{0E4175EF-2B10-4DAA-8B63-F7240A1967AB}"/>
+    <workbookView xWindow="100" yWindow="330" windowWidth="25590" windowHeight="15040" xr2:uid="{0E4175EF-2B10-4DAA-8B63-F7240A1967AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -63,9 +63,6 @@
     <t>H H H T T T</t>
   </si>
   <si>
-    <t>they're equally likely</t>
-  </si>
-  <si>
     <t>Linda is 31 years old, single, outspoken, and very bright. She majored in philosophy. As a student, she was deeply concerned with issues of discrimination and social justice, and also participated in anti-nuclear demonstrations.</t>
   </si>
   <si>
@@ -91,6 +88,9 @@
   </si>
   <si>
     <t>Equally likely</t>
+  </si>
+  <si>
+    <t>equally likely</t>
   </si>
 </sst>
 </file>
@@ -480,41 +480,41 @@
         <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
